--- a/output/graficos_dimensiones/comunal_s_isapre_a_2021_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_s_isapre_a_2021_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:01</t>
+    <t xml:space="preserve">2026-09-09 22:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_isapre_a_2021_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_s_isapre_a_2021_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:53</t>
+    <t xml:space="preserve">2026-09-18 10:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_isapre_a_2021_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_s_isapre_a_2021_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:16</t>
+    <t xml:space="preserve">2026-09-23 12:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -600,7 +600,9 @@
       <c r="C8" s="2" t="n">
         <v>1403</v>
       </c>
-      <c r="D8" s="2"/>
+      <c r="D8" s="2" t="n">
+        <v>2021</v>
+      </c>
       <c r="E8" s="2"/>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_s_isapre_a_2021_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_s_isapre_a_2021_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:19</t>
+    <t xml:space="preserve">2026-10-02 13:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_s_isapre_a_2021_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_s_isapre_a_2021_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:56</t>
+    <t xml:space="preserve">2026-10-05 09:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
